--- a/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
   <si>
     <t>TGL</t>
   </si>
@@ -656,243 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="Q7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E8" s="3">
         <v>13500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>18200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>36000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>21100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>42300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3">
         <v>14800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>67900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>36600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>40100</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E9" s="3">
         <v>13300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>18000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>35700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>15500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>16000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>21100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>42100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>300</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>13300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>29600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>300</v>
+      </c>
+      <c r="E10" s="3">
         <v>200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>200</v>
       </c>
-      <c r="J10" s="3">
-        <v>0</v>
-      </c>
       <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
-        <v>0</v>
-      </c>
       <c r="M10" s="3">
         <v>0</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>8</v>
+      <c r="N10" s="3">
+        <v>0</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>8</v>
@@ -900,20 +909,23 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>1500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>38300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>17200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -934,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -949,32 +962,32 @@
         <v>100</v>
       </c>
       <c r="G12" s="3">
+        <v>100</v>
+      </c>
+      <c r="H12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
       <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>100</v>
       </c>
       <c r="M12" s="3">
         <v>100</v>
       </c>
       <c r="N12" s="3">
+        <v>100</v>
+      </c>
+      <c r="O12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
@@ -990,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,8 +1062,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1094,16 +1113,19 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>93700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1147,19 +1169,22 @@
         <v>0</v>
       </c>
       <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3">
         <v>7200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>15600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>11200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>7800</v>
       </c>
       <c r="E17" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F17" s="3">
         <v>18000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>40700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>23700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>47700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1800</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>26100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>142200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>36400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>-1100</v>
       </c>
       <c r="E18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-2600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-3500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1700</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>-11300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-74300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,120 +1343,127 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-1000</v>
       </c>
       <c r="H20" s="3">
         <v>-1000</v>
       </c>
       <c r="I20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-200</v>
       </c>
       <c r="K20" s="3">
         <v>-200</v>
       </c>
       <c r="L20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>8</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>10800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>-1000</v>
       </c>
       <c r="E21" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1700</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>-6000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-47900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>9600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1443,100 +1482,106 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3">
-        <v>400</v>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>400</v>
       </c>
       <c r="L22" s="3">
+        <v>400</v>
+      </c>
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1700</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>-13900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-64500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1544,11 +1589,11 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -1573,26 +1618,29 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>8</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>3100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>-1200</v>
       </c>
       <c r="E26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1700</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>-17000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-70400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-10500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>-1200</v>
       </c>
       <c r="E27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1700</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>-17000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-70400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-10500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>100</v>
       </c>
       <c r="E32" s="3">
+        <v>200</v>
+      </c>
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1000</v>
       </c>
       <c r="H32" s="3">
         <v>1000</v>
       </c>
       <c r="I32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J32" s="3">
         <v>300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>200</v>
       </c>
       <c r="K32" s="3">
         <v>200</v>
       </c>
       <c r="L32" s="3">
+        <v>200</v>
+      </c>
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>8</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>1800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-10800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>-1200</v>
       </c>
       <c r="E33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1700</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>-17000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-70400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-10500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>-1200</v>
       </c>
       <c r="E35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1700</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>-17000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-70400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-10500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,38 +2397,39 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E41" s="3">
         <v>2600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2356,20 +2442,23 @@
       <c r="P41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R41" s="3">
         <v>44400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>30400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>42600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2424,26 +2513,29 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
       <c r="I43" s="3">
         <v>0</v>
       </c>
@@ -2451,11 +2543,11 @@
         <v>0</v>
       </c>
       <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2468,50 +2560,53 @@
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R43" s="3">
         <v>24500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>60700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="E44" s="3">
         <v>400</v>
       </c>
       <c r="F44" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="G44" s="3">
         <v>200</v>
       </c>
       <c r="H44" s="3">
+        <v>200</v>
+      </c>
+      <c r="I44" s="3">
         <v>100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>200</v>
       </c>
-      <c r="L44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2524,20 +2619,23 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R44" s="3">
         <v>12100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>22500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2545,29 +2643,29 @@
         <v>800</v>
       </c>
       <c r="E45" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="F45" s="3">
         <v>900</v>
       </c>
       <c r="G45" s="3">
+        <v>900</v>
+      </c>
+      <c r="H45" s="3">
         <v>500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2580,49 +2678,52 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>6500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E46" s="3">
         <v>4200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2300</v>
-      </c>
-      <c r="J46" s="3">
-        <v>2000</v>
       </c>
       <c r="K46" s="3">
         <v>2000</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>8</v>
+      <c r="L46" s="3">
+        <v>2000</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>8</v>
@@ -2636,43 +2737,46 @@
       <c r="P46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R46" s="3">
         <v>87500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>109400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>84400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>91600</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>1100</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2704,8 +2808,11 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2716,7 +2823,7 @@
         <v>300</v>
       </c>
       <c r="F48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G48" s="3">
         <v>400</v>
@@ -2725,7 +2832,7 @@
         <v>400</v>
       </c>
       <c r="I48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="J48" s="3">
         <v>300</v>
@@ -2733,8 +2840,8 @@
       <c r="K48" s="3">
         <v>300</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>8</v>
+      <c r="L48" s="3">
+        <v>300</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>8</v>
@@ -2748,43 +2855,46 @@
       <c r="P48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R48" s="3">
         <v>188700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>190500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>257100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>259300</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
+        <v>1600</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2805,19 +2915,22 @@
         <v>0</v>
       </c>
       <c r="Q49" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="R49" s="3">
         <v>700</v>
       </c>
       <c r="S49" s="3">
+        <v>700</v>
+      </c>
+      <c r="T49" s="3">
         <v>43200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>37400</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,34 +3044,37 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="3">
-        <v>0</v>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
         <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>8</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>8</v>
@@ -2972,20 +3091,23 @@
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R52" s="3">
         <v>5100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,38 +3162,41 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E54" s="3">
         <v>5500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2300</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3084,20 +3209,23 @@
       <c r="P54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R54" s="3">
         <v>282100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>307400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>395500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,37 +3269,38 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>200</v>
+      </c>
+      <c r="E57" s="3">
         <v>100</v>
       </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
       <c r="F57" s="3">
         <v>0</v>
       </c>
       <c r="G57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H57" s="3">
         <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K57" s="3">
         <v>600</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
+      <c r="L57" s="3">
+        <v>600</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>8</v>
@@ -3184,49 +3314,52 @@
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R57" s="3">
         <v>41600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>40000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>41200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>3800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2100</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>14800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2200</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -3240,50 +3373,53 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3">
         <v>1200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E59" s="3">
         <v>2500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1500</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1000</v>
       </c>
       <c r="G59" s="3">
         <v>1000</v>
       </c>
       <c r="H59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I59" s="3">
         <v>1100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5800</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3296,50 +3432,53 @@
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
       </c>
       <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
         <v>300</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E60" s="3">
         <v>6400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6400</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3352,20 +3491,23 @@
       <c r="P60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R60" s="3">
         <v>42800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>41500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>43100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3385,17 +3527,17 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>7800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7700</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3409,19 +3551,22 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>35000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>47000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>48300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3440,8 +3585,8 @@
       <c r="H62" s="3">
         <v>0</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
+      <c r="I62" s="3">
+        <v>0</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
@@ -3455,8 +3600,8 @@
       <c r="M62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -3465,19 +3610,22 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+      <c r="R62" s="3">
         <v>21300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>21900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>29000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,38 +3798,41 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6500</v>
+        <v>1200</v>
       </c>
       <c r="E66" s="3">
         <v>6500</v>
       </c>
       <c r="F66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="G66" s="3">
         <v>3100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14200</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>8</v>
       </c>
@@ -3688,20 +3845,23 @@
       <c r="P66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R66" s="3">
         <v>99100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>110400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>120400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>116600</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,38 +4116,41 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-33600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-31400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-28300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-25400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-23400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-19700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-17100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-13900</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>8</v>
       </c>
@@ -3990,20 +4163,23 @@
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R72" s="3">
         <v>-41700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-24600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>46000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,38 +4352,41 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-15600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-14200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-11900</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4214,20 +4399,23 @@
       <c r="P76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R76" s="3">
         <v>183000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>197000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>275100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>284400</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="Q80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>-1200</v>
       </c>
       <c r="E81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1700</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>-17000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-70400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-10500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,13 +4618,14 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
         <v>0</v>
@@ -4436,11 +4634,11 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
       <c r="I83" s="3">
         <v>0</v>
       </c>
@@ -4459,26 +4657,29 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>8</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R83" s="3">
         <v>7200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>15600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>11200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1100</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R89" s="3">
         <v>31300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>30400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,13 +5054,14 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -4856,43 +5076,46 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>8</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q91" s="3">
-        <v>-100</v>
+      <c r="Q91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
       </c>
       <c r="S91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,13 +5229,16 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E94" s="3">
         <v>0</v>
@@ -5018,49 +5247,52 @@
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
       </c>
       <c r="K94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>8</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R94" s="3">
         <v>-3600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-14600</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5313,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5135,10 +5368,13 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,64 +5547,70 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>7800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1400</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R100" s="3">
         <v>-13800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-13300</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5370,107 +5618,113 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H101" s="3">
         <v>-200</v>
       </c>
       <c r="I101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>8</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-1300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R102" s="3">
         <v>14000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>11300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-12400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>TGL</t>
   </si>
@@ -656,255 +656,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E8" s="3">
         <v>6700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>13500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>18200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>36000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>21100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>42300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R8" s="3">
+      <c r="R8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="3">
         <v>14800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>67900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>36600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>40100</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E9" s="3">
         <v>6400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>15200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>18000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>35700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>16000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>42100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>300</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3">
         <v>13300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>29600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>200</v>
+      </c>
+      <c r="E10" s="3">
         <v>300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
       <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
         <v>200</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
-      </c>
       <c r="N10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>8</v>
+      <c r="O10" s="3">
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>8</v>
@@ -912,20 +922,23 @@
       <c r="Q10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>1500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>38300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>17200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,13 +960,14 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E12" s="3">
         <v>100</v>
@@ -965,32 +979,32 @@
         <v>100</v>
       </c>
       <c r="H12" s="3">
+        <v>100</v>
+      </c>
+      <c r="I12" s="3">
         <v>300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
       <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>200</v>
-      </c>
-      <c r="M12" s="3">
-        <v>100</v>
       </c>
       <c r="N12" s="3">
         <v>100</v>
       </c>
       <c r="O12" s="3">
+        <v>100</v>
+      </c>
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,8 +1082,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1116,16 +1136,19 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>93700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1172,19 +1195,22 @@
         <v>0</v>
       </c>
       <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
         <v>7200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>15600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>11200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>21000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>40700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>23700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>47700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1800</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3">
         <v>26100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>142200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>36400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-2800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-4700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-3500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1700</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3">
         <v>-11300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-74300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,126 +1377,133 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-1000</v>
       </c>
       <c r="I20" s="3">
         <v>-1000</v>
       </c>
       <c r="J20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-200</v>
       </c>
       <c r="L20" s="3">
         <v>-200</v>
       </c>
       <c r="M20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>8</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>10800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1700</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="3">
         <v>-6000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-47900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1485,103 +1525,109 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K22" s="3">
-        <v>400</v>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>400</v>
       </c>
       <c r="M22" s="3">
+        <v>400</v>
+      </c>
+      <c r="N22" s="3">
         <v>100</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-2900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1700</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="3">
         <v>-13900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-64500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1592,11 +1638,11 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
@@ -1621,26 +1667,29 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>8</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="3">
         <v>3100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-2900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1700</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="3">
         <v>-17000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-70400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-10500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1700</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="3">
         <v>-17000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-70400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-10500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2119,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>300</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1000</v>
       </c>
       <c r="I32" s="3">
         <v>1000</v>
       </c>
       <c r="J32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>200</v>
       </c>
       <c r="L32" s="3">
         <v>200</v>
       </c>
       <c r="M32" s="3">
+        <v>200</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>8</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S32" s="3">
         <v>1800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-10800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1700</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S33" s="3">
         <v>-17000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-70400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-10500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1700</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S35" s="3">
         <v>-17000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-70400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-10500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="R38" s="2">
+      <c r="R38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,41 +2484,42 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1600</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2445,20 +2532,23 @@
       <c r="Q41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S41" s="3">
         <v>44400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>30400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>42600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2516,13 +2606,16 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>200</v>
@@ -2531,14 +2624,14 @@
         <v>200</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
         <v>0</v>
       </c>
@@ -2546,11 +2639,11 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>200</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2563,53 +2656,56 @@
       <c r="Q43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S43" s="3">
         <v>24500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>60700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
         <v>100</v>
-      </c>
-      <c r="E44" s="3">
-        <v>400</v>
       </c>
       <c r="F44" s="3">
         <v>400</v>
       </c>
       <c r="G44" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H44" s="3">
         <v>200</v>
       </c>
       <c r="I44" s="3">
+        <v>200</v>
+      </c>
+      <c r="J44" s="3">
         <v>100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>200</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2622,20 +2718,23 @@
       <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R44" s="3">
+      <c r="R44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S44" s="3">
         <v>12100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>22500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2643,32 +2742,32 @@
         <v>800</v>
       </c>
       <c r="E45" s="3">
+        <v>800</v>
+      </c>
+      <c r="F45" s="3">
         <v>1000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>900</v>
       </c>
       <c r="G45" s="3">
         <v>900</v>
       </c>
       <c r="H45" s="3">
+        <v>900</v>
+      </c>
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2681,52 +2780,55 @@
       <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S45" s="3">
         <v>6500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>10500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E46" s="3">
         <v>2400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2300</v>
-      </c>
-      <c r="K46" s="3">
-        <v>2000</v>
       </c>
       <c r="L46" s="3">
         <v>2000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>8</v>
+      <c r="M46" s="3">
+        <v>2000</v>
       </c>
       <c r="N46" s="3" t="s">
         <v>8</v>
@@ -2740,32 +2842,35 @@
       <c r="Q46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S46" s="3">
         <v>87500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>109400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>84400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>91600</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>300</v>
+      </c>
+      <c r="E47" s="3">
         <v>600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1100</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2778,8 +2883,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2811,13 +2916,16 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E48" s="3">
         <v>300</v>
@@ -2826,7 +2934,7 @@
         <v>300</v>
       </c>
       <c r="G48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H48" s="3">
         <v>400</v>
@@ -2835,7 +2943,7 @@
         <v>400</v>
       </c>
       <c r="J48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="K48" s="3">
         <v>300</v>
@@ -2843,8 +2951,8 @@
       <c r="L48" s="3">
         <v>300</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>8</v>
+      <c r="M48" s="3">
+        <v>300</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>8</v>
@@ -2858,29 +2966,32 @@
       <c r="Q48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R48" s="3">
+      <c r="R48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S48" s="3">
         <v>188700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>190500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>257100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>259300</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E49" s="3">
         <v>1600</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F49" s="3" t="s">
         <v>8</v>
       </c>
@@ -2896,8 +3007,8 @@
       <c r="J49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
+      <c r="K49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L49" s="3">
         <v>0</v>
@@ -2918,19 +3029,22 @@
         <v>0</v>
       </c>
       <c r="R49" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="S49" s="3">
         <v>700</v>
       </c>
       <c r="T49" s="3">
+        <v>700</v>
+      </c>
+      <c r="U49" s="3">
         <v>43200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>37400</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,8 +3164,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3058,26 +3178,26 @@
       <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>8</v>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>8</v>
@@ -3094,20 +3214,23 @@
       <c r="Q52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S52" s="3">
         <v>5100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,41 +3288,44 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E54" s="3">
         <v>4900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2300</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3212,20 +3338,23 @@
       <c r="Q54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S54" s="3">
         <v>282100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>307400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>395500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,8 +3400,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3279,31 +3410,31 @@
         <v>200</v>
       </c>
       <c r="E57" s="3">
+        <v>200</v>
+      </c>
+      <c r="F57" s="3">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
       <c r="G57" s="3">
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>8</v>
+      <c r="M57" s="3">
+        <v>600</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>8</v>
@@ -3317,52 +3448,55 @@
       <c r="Q57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S57" s="3">
         <v>41600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>40000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>41200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>3800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2100</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>14800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
@@ -3376,53 +3510,56 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S58" s="3">
         <v>1200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>800</v>
+      </c>
+      <c r="E59" s="3">
         <v>1100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1000</v>
       </c>
       <c r="H59" s="3">
         <v>1000</v>
       </c>
       <c r="I59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J59" s="3">
         <v>1100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5800</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3435,53 +3572,56 @@
       <c r="Q59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
+      <c r="R59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
       </c>
       <c r="T59" s="3">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3">
         <v>300</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6400</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3494,20 +3634,23 @@
       <c r="Q60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S60" s="3">
         <v>42800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>41500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>43100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3530,17 +3673,17 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3554,19 +3697,22 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>35000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>47000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>48300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3588,8 +3734,8 @@
       <c r="I62" s="3">
         <v>0</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
+      <c r="J62" s="3">
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
@@ -3603,8 +3749,8 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -3613,19 +3759,22 @@
         <v>0</v>
       </c>
       <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
         <v>21300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>29000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,41 +3956,44 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1200</v>
-      </c>
-      <c r="E66" s="3">
-        <v>6500</v>
       </c>
       <c r="F66" s="3">
         <v>6500</v>
       </c>
       <c r="G66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H66" s="3">
         <v>3100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>18300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14200</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>8</v>
       </c>
@@ -3848,20 +4006,23 @@
       <c r="Q66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S66" s="3">
         <v>99100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>110400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>120400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>116600</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,41 +4290,44 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-34800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-33600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-31400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-28300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-25400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-23400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-19700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-17100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-13900</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4166,20 +4340,23 @@
       <c r="Q72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S72" s="3">
         <v>-41700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-24600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>46000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,41 +4538,44 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E76" s="3">
         <v>3700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-15600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-14200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-11900</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4402,20 +4588,23 @@
       <c r="Q76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S76" s="3">
         <v>183000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>197000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>275100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>284400</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="R80" s="2">
+      <c r="R80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1700</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S81" s="3">
         <v>-17000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-70400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-10500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,8 +4817,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4628,7 +4827,7 @@
         <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -4637,11 +4836,11 @@
         <v>0</v>
       </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
       <c r="J83" s="3">
         <v>0</v>
       </c>
@@ -4660,26 +4859,29 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>8</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S83" s="3">
         <v>7200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>15600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>11200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1100</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S89" s="3">
         <v>31300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-4700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>30400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,17 +5275,18 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
@@ -5079,43 +5300,46 @@
         <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>8</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R91" s="3">
-        <v>-100</v>
+      <c r="R91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S91" s="3">
         <v>-100</v>
       </c>
       <c r="T91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U91" s="3">
         <v>-600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,17 +5459,20 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -5250,49 +5480,52 @@
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K94" s="3">
         <v>-100</v>
       </c>
       <c r="L94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>8</v>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S94" s="3">
         <v>-3600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-14600</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,8 +5547,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5371,10 +5605,13 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,181 +5793,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>7700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>7800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1400</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S100" s="3">
         <v>-13800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-8000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-13300</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3">
         <v>-200</v>
       </c>
       <c r="J101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>8</v>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>5200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-1300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S102" s="3">
         <v>14000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>11300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-12400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>TGL</t>
   </si>
@@ -656,227 +656,247 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S7" s="2">
+      <c r="S7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
         <v>1600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>6700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>13500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>15300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>18200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>36000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>15600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>16200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>21100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>42300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>13600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U8" s="3">
         <v>14800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>67900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>36600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>40100</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>200</v>
+      </c>
+      <c r="F9" s="3">
         <v>1400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>6400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>13300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>15200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>18000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>35700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>15500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>16000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>21100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>42100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>13600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U9" s="3">
         <v>13300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>29600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>19400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -884,28 +904,28 @@
         <v>200</v>
       </c>
       <c r="E10" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
         <v>200</v>
       </c>
       <c r="G10" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="H10" s="3">
         <v>200</v>
       </c>
       <c r="I10" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3">
         <v>100</v>
       </c>
       <c r="K10" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" s="3">
         <v>200</v>
@@ -914,31 +934,37 @@
         <v>0</v>
       </c>
       <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>8</v>
+        <v>200</v>
+      </c>
+      <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U10" s="3">
         <v>1500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>38300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>17200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,19 +987,21 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3">
         <v>100</v>
       </c>
       <c r="F12" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G12" s="3">
         <v>100</v>
@@ -982,35 +1010,35 @@
         <v>100</v>
       </c>
       <c r="I12" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3">
         <v>100</v>
       </c>
       <c r="K12" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L12" s="3">
         <v>100</v>
       </c>
       <c r="M12" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="N12" s="3">
         <v>100</v>
       </c>
       <c r="O12" s="3">
+        <v>200</v>
+      </c>
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
+        <v>100</v>
+      </c>
+      <c r="R12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1023,8 +1051,14 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,31 +1119,37 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1139,16 +1179,22 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>93700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1198,19 +1244,25 @@
         <v>0</v>
       </c>
       <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
         <v>7200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>15600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>11200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1282,146 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F17" s="3">
         <v>3000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>7800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>15400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>18000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>21000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>40700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>18200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>18500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>23700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>47700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>17100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1800</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U17" s="3">
         <v>26100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>142200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>36400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-2700</v>
       </c>
-      <c r="H18" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-4700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-2300</v>
       </c>
       <c r="L18" s="3">
         <v>-2600</v>
       </c>
       <c r="M18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="O18" s="3">
         <v>-5400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-3500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-2400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U18" s="3">
         <v>-11300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-74300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,132 +1444,146 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="N20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U20" s="3">
         <v>-1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>10800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1500</v>
+        <v>-800</v>
       </c>
       <c r="E21" s="3">
-        <v>-1000</v>
+        <v>-1700</v>
       </c>
       <c r="F21" s="3">
-        <v>-2000</v>
+        <v>-1300</v>
       </c>
       <c r="G21" s="3">
-        <v>-3000</v>
+        <v>-300</v>
       </c>
       <c r="H21" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="J21" s="3">
         <v>-2900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-5600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-2500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-2800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-5500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-3600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-2500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U21" s="3">
         <v>-6000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-47900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>9600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1528,106 +1608,118 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U22" s="3">
         <v>800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>1000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>1200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-2100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-5700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-2600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-5900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-3700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U23" s="3">
         <v>-13900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-64500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1637,18 +1729,18 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1670,26 +1762,32 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U24" s="3">
         <v>3100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>5800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>7700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1848,150 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F26" s="3">
         <v>-1700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-2100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-5900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-3700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-2500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U26" s="3">
         <v>-17000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-70400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-10500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-2100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-5900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-3700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-2500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U27" s="3">
         <v>-17000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-70400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-10500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +2052,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2120,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2188,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2256,150 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>700</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="N32" s="3">
+        <v>200</v>
+      </c>
+      <c r="O32" s="3">
+        <v>200</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J32" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>300</v>
-      </c>
-      <c r="L32" s="3">
-        <v>200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>200</v>
-      </c>
-      <c r="N32" s="3">
-        <v>100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U32" s="3">
         <v>1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-10800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-2100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-5900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-3700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-2500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U33" s="3">
         <v>-17000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-70400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-10500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2460,155 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-2100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-5900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-3700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-2500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U35" s="3">
         <v>-17000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-70400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-10500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S38" s="2">
+      <c r="S38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2631,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,47 +2657,49 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>200</v>
+      </c>
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1600</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2535,40 +2709,46 @@
       <c r="R41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U41" s="3">
         <v>44400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>30400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>42600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2609,47 +2789,53 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" s="3">
         <v>100</v>
-      </c>
-      <c r="E43" s="3">
-        <v>200</v>
-      </c>
-      <c r="F43" s="3">
-        <v>200</v>
       </c>
       <c r="G43" s="3">
         <v>200</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I43" s="3">
+        <v>200</v>
+      </c>
+      <c r="J43" s="3">
+        <v>500</v>
+      </c>
+      <c r="K43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>200</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2659,20 +2845,26 @@
       <c r="R43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U43" s="3">
         <v>24500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>60700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>13700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2680,22 +2872,22 @@
         <v>0</v>
       </c>
       <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
         <v>100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>200</v>
-      </c>
-      <c r="I44" s="3">
-        <v>200</v>
-      </c>
-      <c r="J44" s="3">
-        <v>100</v>
       </c>
       <c r="K44" s="3">
         <v>200</v>
@@ -2706,11 +2898,11 @@
       <c r="M44" s="3">
         <v>200</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>8</v>
+      <c r="N44" s="3">
+        <v>100</v>
+      </c>
+      <c r="O44" s="3">
+        <v>200</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>8</v>
@@ -2721,59 +2913,65 @@
       <c r="R44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S44" s="3">
+      <c r="S44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U44" s="3">
         <v>12100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>7900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>22500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="E45" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="F45" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G45" s="3">
+        <v>500</v>
+      </c>
+      <c r="H45" s="3">
+        <v>500</v>
+      </c>
+      <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>400</v>
+      </c>
+      <c r="K45" s="3">
+        <v>500</v>
+      </c>
+      <c r="L45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3">
-        <v>900</v>
-      </c>
-      <c r="I45" s="3">
-        <v>500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>900</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2783,20 +2981,26 @@
       <c r="R45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U45" s="3">
         <v>6500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>10500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>5600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2804,38 +3008,38 @@
         <v>1200</v>
       </c>
       <c r="E46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G46" s="3">
         <v>2400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>2000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>8</v>
       </c>
@@ -2845,38 +3049,44 @@
       <c r="R46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U46" s="3">
         <v>87500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>109400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>84400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>91600</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>1100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
@@ -2886,11 +3096,11 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -2919,8 +3129,14 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2928,37 +3144,37 @@
         <v>200</v>
       </c>
       <c r="E48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G48" s="3">
         <v>300</v>
       </c>
       <c r="H48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J48" s="3">
         <v>400</v>
       </c>
       <c r="K48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M48" s="3">
         <v>300</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>8</v>
+      <c r="N48" s="3">
+        <v>300</v>
+      </c>
+      <c r="O48" s="3">
+        <v>300</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>8</v>
@@ -2969,52 +3185,58 @@
       <c r="R48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U48" s="3">
         <v>188700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>190500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>257100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>259300</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F49" s="3">
         <v>2400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1600</v>
       </c>
-      <c r="F49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>8</v>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -3032,19 +3254,25 @@
         <v>0</v>
       </c>
       <c r="S49" s="3">
+        <v>0</v>
+      </c>
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
         <v>700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>43200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>37400</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3333,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,13 +3401,19 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>1500</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>8</v>
@@ -3181,17 +3421,17 @@
       <c r="F52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
-      </c>
-      <c r="I52" s="3">
-        <v>100</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -3199,11 +3439,11 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>8</v>
+      <c r="M52" s="3">
+        <v>100</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>8</v>
@@ -3217,20 +3457,26 @@
       <c r="R52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U52" s="3">
         <v>5100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>6800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>10800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,47 +3537,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F54" s="3">
         <v>4200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>4900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>5500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>6400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>5700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>6200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>8400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2300</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3341,20 +3593,26 @@
       <c r="R54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U54" s="3">
         <v>282100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>307400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>395500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3635,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,47 +3661,49 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>100</v>
       </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
       <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>100</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
@@ -3451,58 +3713,64 @@
       <c r="R57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U57" s="3">
         <v>41600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>40000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>41200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>100</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
-        <v>3800</v>
+        <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
-        <v>2100</v>
+        <v>4200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>14800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2200</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
@@ -3513,59 +3781,65 @@
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U58" s="3">
         <v>1200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>1500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>500</v>
+      </c>
+      <c r="G59" s="3">
+        <v>700</v>
+      </c>
+      <c r="H59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>300</v>
+      </c>
+      <c r="K59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
-        <v>2500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>6000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5800</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3575,59 +3849,65 @@
       <c r="R59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
-      <c r="T59" s="3">
-        <v>0</v>
+      <c r="S59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U59" s="3">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="3">
         <v>300</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>900</v>
+      </c>
+      <c r="F60" s="3">
         <v>1100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>18200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>8800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6400</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3637,20 +3917,26 @@
       <c r="R60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U60" s="3">
         <v>42800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>41500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>43100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3676,20 +3962,20 @@
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>7800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7700</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3700,48 +3986,54 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>35000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>47000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>48300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>8</v>
@@ -3752,29 +4044,35 @@
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
         <v>21300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>21900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>29000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +4133,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4201,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,47 +4269,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>900</v>
+      </c>
+      <c r="F66" s="3">
         <v>1100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>18300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>16600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>14200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4009,20 +4325,26 @@
       <c r="R66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U66" s="3">
         <v>99100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>110400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>120400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>116600</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4367,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4431,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4499,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4567,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,47 +4635,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="F72" s="3">
         <v>-36500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-34800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-33600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-31400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-28300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-25400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-23400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-19700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-17100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-13900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4343,20 +4691,26 @@
       <c r="R72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U72" s="3">
         <v>-41700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-24600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>46000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4771,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4839,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,47 +4907,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F76" s="3">
         <v>3100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>7100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-15600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-14200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-11900</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4591,20 +4963,26 @@
       <c r="R76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U76" s="3">
         <v>183000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>197000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>275100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>284400</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +5043,155 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S80" s="2">
+      <c r="S80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-2100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-5900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-3700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-2500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U81" s="3">
         <v>-17000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-70400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-10500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,16 +5214,18 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -4839,14 +5237,14 @@
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -4862,26 +5260,32 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U83" s="3">
         <v>7200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>15600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>11200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5346,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5414,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5482,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5550,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5618,82 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-1100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-2500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-2400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-2700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-2100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-3800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-4400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U89" s="3">
         <v>31300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-4700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>30400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,70 +5716,78 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-600</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X91" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5848,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,28 +5916,34 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-1500</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
       <c r="H94" s="3">
         <v>0</v>
       </c>
       <c r="I94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J94" s="3">
         <v>0</v>
@@ -5492,40 +5952,46 @@
         <v>-100</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U94" s="3">
         <v>-3600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-5900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-11300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-14600</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,31 +6014,33 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5608,10 +6076,16 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +6146,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +6214,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,190 +6282,214 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>300</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>3100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>7700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>7800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>3200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>2100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>2800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>5900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>2500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1400</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U100" s="3">
         <v>-13800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-8000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-13300</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>100</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S101" s="3">
-        <v>100</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-200</v>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U101" s="3">
         <v>100</v>
       </c>
       <c r="V101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+        <v>-200</v>
+      </c>
+      <c r="W101" s="3">
+        <v>100</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-1400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>2900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>5200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-1300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>1600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U102" s="3">
         <v>14000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-12000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>11300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-12400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
   <si>
     <t>TGL</t>
   </si>
@@ -656,247 +656,256 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="U7" s="2">
+      <c r="U7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>18200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>36000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>21100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>42300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>100</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V8" s="3">
         <v>14800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>67900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>36600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>40100</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
         <v>200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>15200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>18000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>35700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>15500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>42100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>13600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>300</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V9" s="3">
         <v>13300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>29600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -904,46 +913,46 @@
         <v>200</v>
       </c>
       <c r="E10" s="3">
+        <v>200</v>
+      </c>
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>100</v>
       </c>
       <c r="J10" s="3">
         <v>100</v>
       </c>
       <c r="K10" s="3">
+        <v>100</v>
+      </c>
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>200</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
       <c r="O10" s="3">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3">
         <v>200</v>
       </c>
-      <c r="P10" s="3">
-        <v>0</v>
-      </c>
       <c r="Q10" s="3">
         <v>0</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>8</v>
+      <c r="R10" s="3">
+        <v>0</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>8</v>
@@ -951,20 +960,23 @@
       <c r="T10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V10" s="3">
         <v>1500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>38300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>17200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -989,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -998,13 +1011,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>100</v>
       </c>
       <c r="H12" s="3">
         <v>100</v>
@@ -1016,32 +1029,32 @@
         <v>100</v>
       </c>
       <c r="K12" s="3">
+        <v>100</v>
+      </c>
+      <c r="L12" s="3">
         <v>300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
       <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>200</v>
-      </c>
-      <c r="P12" s="3">
-        <v>100</v>
       </c>
       <c r="Q12" s="3">
         <v>100</v>
       </c>
       <c r="R12" s="3">
+        <v>100</v>
+      </c>
+      <c r="S12" s="3">
         <v>200</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1057,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1125,34 +1141,37 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
-        <v>700</v>
-      </c>
       <c r="H14" s="3">
+        <v>400</v>
+      </c>
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1185,16 +1204,19 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>93700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1250,19 +1272,22 @@
         <v>0</v>
       </c>
       <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
         <v>7200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>15600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>11200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1284,8 +1309,9 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1293,135 +1319,141 @@
         <v>1000</v>
       </c>
       <c r="E17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>15400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>40700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>23700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>47700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>17100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1800</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V17" s="3">
         <v>26100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>142200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>36400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-2700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-2600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1700</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V18" s="3">
         <v>-11300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-74300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1446,8 +1478,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1461,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1473,117 +1506,123 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>-1000</v>
       </c>
       <c r="M20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N20" s="3">
         <v>-300</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-200</v>
       </c>
       <c r="O20" s="3">
         <v>-200</v>
       </c>
       <c r="P20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>8</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>10800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1300</v>
       </c>
-      <c r="G21" s="3">
-        <v>-300</v>
-      </c>
       <c r="H21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-5600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1700</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3">
         <v>-6000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-47900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1614,112 +1653,118 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3">
-        <v>400</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O22" s="3">
         <v>400</v>
       </c>
       <c r="P22" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V22" s="3">
         <v>800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-2100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1700</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V23" s="3">
         <v>-13900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-64500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1729,21 +1774,21 @@
       <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1768,26 +1813,29 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>8</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V24" s="3">
         <v>3100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1854,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-3700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1700</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V26" s="3">
         <v>-17000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-70400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-3700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1700</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V27" s="3">
         <v>-17000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-70400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2058,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2126,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2194,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2262,8 +2328,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2277,10 +2346,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -2289,117 +2358,123 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>1000</v>
       </c>
       <c r="M32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="N32" s="3">
         <v>300</v>
-      </c>
-      <c r="N32" s="3">
-        <v>200</v>
       </c>
       <c r="O32" s="3">
         <v>200</v>
       </c>
       <c r="P32" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>8</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V32" s="3">
         <v>1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-10800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-2900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-3700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1700</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V33" s="3">
         <v>-17000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-70400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2466,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-2900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-3700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1700</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V35" s="3">
         <v>-17000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-70400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="U38" s="2">
+      <c r="U38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2633,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2659,50 +2744,51 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1600</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2715,31 +2801,34 @@
       <c r="T41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V41" s="3">
         <v>44400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>30400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>42600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>500</v>
+      </c>
+      <c r="E42" s="3">
         <v>200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>400</v>
-      </c>
-      <c r="F42" s="3">
-        <v>100</v>
       </c>
       <c r="G42" s="3">
         <v>100</v>
@@ -2751,7 +2840,7 @@
         <v>100</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2795,22 +2884,25 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
+      <c r="D43" s="3">
+        <v>1100</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
         <v>100</v>
-      </c>
-      <c r="G43" s="3">
-        <v>200</v>
       </c>
       <c r="H43" s="3">
         <v>200</v>
@@ -2819,14 +2911,14 @@
         <v>200</v>
       </c>
       <c r="J43" s="3">
+        <v>200</v>
+      </c>
+      <c r="K43" s="3">
         <v>500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2834,11 +2926,11 @@
         <v>0</v>
       </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2851,20 +2943,23 @@
       <c r="T43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V43" s="3">
         <v>24500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>60700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2878,35 +2973,35 @@
         <v>0</v>
       </c>
       <c r="G44" s="3">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3">
         <v>100</v>
-      </c>
-      <c r="H44" s="3">
-        <v>400</v>
       </c>
       <c r="I44" s="3">
         <v>400</v>
       </c>
       <c r="J44" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K44" s="3">
         <v>200</v>
       </c>
       <c r="L44" s="3">
+        <v>200</v>
+      </c>
+      <c r="M44" s="3">
         <v>100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>200</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
@@ -2919,31 +3014,34 @@
       <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U44" s="3">
+      <c r="U44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V44" s="3">
         <v>12100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>22500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>300</v>
+      </c>
+      <c r="E45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>500</v>
       </c>
       <c r="G45" s="3">
         <v>500</v>
@@ -2952,29 +3050,29 @@
         <v>500</v>
       </c>
       <c r="I45" s="3">
+        <v>500</v>
+      </c>
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2987,61 +3085,64 @@
       <c r="T45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U45" s="3">
+      <c r="U45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V45" s="3">
         <v>6500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>10500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2300</v>
-      </c>
-      <c r="N46" s="3">
-        <v>2000</v>
       </c>
       <c r="O46" s="3">
         <v>2000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>8</v>
+      <c r="P46" s="3">
+        <v>2000</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>8</v>
@@ -3055,20 +3156,23 @@
       <c r="T46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V46" s="3">
         <v>87500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>109400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>84400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>91600</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3078,18 +3182,18 @@
       <c r="E47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1100</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3102,8 +3206,8 @@
       <c r="M47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
@@ -3135,13 +3239,16 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3">
         <v>200</v>
@@ -3150,7 +3257,7 @@
         <v>200</v>
       </c>
       <c r="G48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H48" s="3">
         <v>300</v>
@@ -3159,7 +3266,7 @@
         <v>300</v>
       </c>
       <c r="J48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K48" s="3">
         <v>400</v>
@@ -3168,7 +3275,7 @@
         <v>400</v>
       </c>
       <c r="M48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N48" s="3">
         <v>300</v>
@@ -3176,8 +3283,8 @@
       <c r="O48" s="3">
         <v>300</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>8</v>
+      <c r="P48" s="3">
+        <v>300</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>8</v>
@@ -3191,46 +3298,49 @@
       <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V48" s="3">
         <v>188700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>190500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>257100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>259300</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E49" s="3">
         <v>4200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1600</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>8</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>8</v>
@@ -3238,8 +3348,8 @@
       <c r="M49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
+      <c r="N49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
@@ -3260,19 +3370,22 @@
         <v>0</v>
       </c>
       <c r="U49" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="V49" s="3">
         <v>700</v>
       </c>
       <c r="W49" s="3">
+        <v>700</v>
+      </c>
+      <c r="X49" s="3">
         <v>43200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>37400</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3339,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3407,17 +3523,20 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E52" s="3">
         <v>1500</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3430,23 +3549,23 @@
       <c r="I52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="3">
-        <v>100</v>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>8</v>
+      <c r="O52" s="3">
+        <v>0</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>8</v>
@@ -3463,20 +3582,23 @@
       <c r="T52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V52" s="3">
         <v>5100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3543,50 +3665,53 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E54" s="3">
         <v>7100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>4300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2300</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3599,20 +3724,23 @@
       <c r="T54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V54" s="3">
         <v>282100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>307400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>395500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3637,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3663,8 +3792,9 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3675,37 +3805,37 @@
         <v>0</v>
       </c>
       <c r="F57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G57" s="3">
         <v>200</v>
       </c>
       <c r="H57" s="3">
+        <v>200</v>
+      </c>
+      <c r="I57" s="3">
         <v>100</v>
       </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K57" s="3">
-        <v>100</v>
+      <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L57" s="3">
         <v>100</v>
       </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N57" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>8</v>
+      <c r="P57" s="3">
+        <v>600</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>8</v>
@@ -3719,20 +3849,23 @@
       <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V57" s="3">
         <v>41600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>40000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>41200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3740,40 +3873,40 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>4200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>14800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2200</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
@@ -3787,25 +3920,28 @@
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V58" s="3">
         <v>1200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E59" s="3">
         <v>500</v>
@@ -3814,35 +3950,35 @@
         <v>500</v>
       </c>
       <c r="G59" s="3">
+        <v>500</v>
+      </c>
+      <c r="H59" s="3">
         <v>700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5800</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3855,62 +3991,65 @@
       <c r="T59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
+      <c r="U59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
       </c>
       <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="3">
         <v>300</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>700</v>
+      </c>
+      <c r="E60" s="3">
         <v>800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>18200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6400</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>8</v>
       </c>
@@ -3923,20 +4062,23 @@
       <c r="T60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V60" s="3">
         <v>42800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>41500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>43100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3968,17 +4110,17 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>7800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7700</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3992,19 +4134,22 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>35000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>47000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>48300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4029,14 +4174,14 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>8</v>
+      <c r="M62" s="3">
+        <v>0</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>8</v>
@@ -4050,8 +4195,8 @@
       <c r="Q62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
+      <c r="R62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S62" s="3">
         <v>0</v>
@@ -4060,19 +4205,22 @@
         <v>0</v>
       </c>
       <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
         <v>21300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>21900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>29000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4139,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4207,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4275,50 +4429,53 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>700</v>
+      </c>
+      <c r="E66" s="3">
         <v>800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1200</v>
-      </c>
-      <c r="H66" s="3">
-        <v>6500</v>
       </c>
       <c r="I66" s="3">
         <v>6500</v>
       </c>
       <c r="J66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K66" s="3">
         <v>3100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14200</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4331,20 +4488,23 @@
       <c r="T66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V66" s="3">
         <v>99100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>110400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>120400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>116600</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4369,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4437,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4505,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4573,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4641,50 +4811,53 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-39200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-39000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-38000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-36500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-34800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-33600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-31400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-28300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-25400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-23400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-19700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-17100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-13900</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4697,20 +4870,23 @@
       <c r="T72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V72" s="3">
         <v>-41700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-24600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>46000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4777,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4845,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4913,50 +5095,53 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E76" s="3">
         <v>6300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-15600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-14200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-11900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>8</v>
       </c>
@@ -4969,20 +5154,23 @@
       <c r="T76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V76" s="3">
         <v>183000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>197000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>275100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>284400</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5049,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="U80" s="2">
+      <c r="U80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-2900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-3700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1700</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V81" s="3">
         <v>-17000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-70400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5216,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5243,11 +5441,11 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -5266,26 +5464,29 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>8</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V83" s="3">
         <v>7200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>15600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>11200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5352,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5420,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5488,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5556,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5624,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1100</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V89" s="3">
         <v>31300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>30400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5718,16 +5937,17 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -5751,43 +5971,46 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>8</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U91" s="3">
-        <v>-100</v>
+      <c r="U91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V91" s="3">
         <v>-100</v>
       </c>
       <c r="W91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X91" s="3">
         <v>-600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5854,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5922,26 +6148,29 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1500</v>
       </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
       <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
       <c r="I94" s="3">
         <v>0</v>
       </c>
@@ -5949,49 +6178,52 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
       </c>
       <c r="O94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>8</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V94" s="3">
         <v>-3600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-11300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-14600</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6016,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6042,8 +6275,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6082,10 +6315,13 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6152,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6220,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6288,76 +6530,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E100" s="3">
         <v>2400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>100</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>5900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1400</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V100" s="3">
         <v>-13800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-8000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-13300</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6365,131 +6613,137 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="L101" s="3">
         <v>-200</v>
       </c>
       <c r="M101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>8</v>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="E102" s="3">
         <v>-100</v>
       </c>
       <c r="F102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>5200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-1300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V102" s="3">
         <v>14000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-12000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>11300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-12400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
   <si>
     <t>TGL</t>
   </si>
@@ -656,306 +656,316 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="V7" s="2">
+      <c r="V7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>700</v>
+      </c>
+      <c r="E8" s="3">
         <v>300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>18200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>36000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>21100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>42300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>100</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V8" s="3">
+      <c r="V8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W8" s="3">
         <v>14800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>67900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>36600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>40100</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>200</v>
+      </c>
+      <c r="E9" s="3">
         <v>100</v>
       </c>
-      <c r="E9" s="3">
-        <v>0</v>
-      </c>
       <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
         <v>200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>15200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>35700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>21100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>42100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>13600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>300</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W9" s="3">
         <v>13300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>29600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E10" s="3">
         <v>200</v>
       </c>
       <c r="F10" s="3">
+        <v>200</v>
+      </c>
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>100</v>
       </c>
       <c r="K10" s="3">
         <v>100</v>
       </c>
       <c r="L10" s="3">
+        <v>100</v>
+      </c>
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>200</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
       <c r="P10" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3">
         <v>200</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
       <c r="R10" s="3">
         <v>0</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>8</v>
+      <c r="S10" s="3">
+        <v>0</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>8</v>
@@ -963,20 +973,23 @@
       <c r="U10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W10" s="3">
         <v>1500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>38300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>17200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,8 +1015,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,13 +1028,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>100</v>
       </c>
       <c r="I12" s="3">
         <v>100</v>
@@ -1032,32 +1046,32 @@
         <v>100</v>
       </c>
       <c r="L12" s="3">
+        <v>100</v>
+      </c>
+      <c r="M12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
-        <v>0</v>
-      </c>
       <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>200</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>100</v>
       </c>
       <c r="R12" s="3">
         <v>100</v>
       </c>
       <c r="S12" s="3">
+        <v>100</v>
+      </c>
+      <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,37 +1161,40 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1207,21 +1227,24 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>93700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1275,19 +1298,22 @@
         <v>0</v>
       </c>
       <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
         <v>7200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>15600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>11200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="E17" s="3">
         <v>1000</v>
       </c>
       <c r="F17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="3">
         <v>2000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>40700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>47700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>17100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W17" s="3">
         <v>26100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>142200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>36400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
         <v>-700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-2900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-3500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1700</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W18" s="3">
         <v>-11300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-74300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,13 +1512,14 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-1800</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1497,11 +1531,11 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1509,120 +1543,126 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>-1000</v>
       </c>
       <c r="N20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-200</v>
       </c>
       <c r="P20" s="3">
         <v>-200</v>
       </c>
       <c r="Q20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>8</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>10800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-5600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1700</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W21" s="3">
         <v>-6000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-47900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>9600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1656,120 +1696,126 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O22" s="3">
-        <v>400</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
         <v>400</v>
       </c>
       <c r="Q22" s="3">
+        <v>400</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
         <v>800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>1000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-2100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1700</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W23" s="3">
         <v>-13900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-64500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1777,21 +1823,21 @@
       <c r="F24" s="3">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1816,26 +1862,29 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>8</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W24" s="3">
         <v>3100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1700</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W26" s="3">
         <v>-17000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-70400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1700</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W27" s="3">
         <v>-17000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-70400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2176,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2189,8 +2250,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,13 +2398,16 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2349,11 +2419,11 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2361,120 +2431,126 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>1000</v>
       </c>
       <c r="N32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
-      </c>
-      <c r="O32" s="3">
-        <v>200</v>
       </c>
       <c r="P32" s="3">
         <v>200</v>
       </c>
       <c r="Q32" s="3">
+        <v>200</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>8</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W32" s="3">
         <v>1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-10800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-2100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-2900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1700</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W33" s="3">
         <v>-17000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-70400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-2100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-2900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1700</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W35" s="3">
         <v>-17000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-70400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="V38" s="2">
+      <c r="V38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,8 +2831,9 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2754,44 +2841,44 @@
         <v>300</v>
       </c>
       <c r="E41" s="3">
+        <v>300</v>
+      </c>
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>8</v>
       </c>
@@ -2804,34 +2891,37 @@
       <c r="U41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W41" s="3">
         <v>44400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>30400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>42600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>400</v>
-      </c>
-      <c r="G42" s="3">
-        <v>100</v>
       </c>
       <c r="H42" s="3">
         <v>100</v>
@@ -2843,7 +2933,7 @@
         <v>100</v>
       </c>
       <c r="K42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -2887,25 +2977,28 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1100</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" s="3">
         <v>100</v>
-      </c>
-      <c r="H43" s="3">
-        <v>200</v>
       </c>
       <c r="I43" s="3">
         <v>200</v>
@@ -2914,14 +3007,14 @@
         <v>200</v>
       </c>
       <c r="K43" s="3">
+        <v>200</v>
+      </c>
+      <c r="L43" s="3">
         <v>500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -2929,11 +3022,11 @@
         <v>0</v>
       </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>8</v>
       </c>
@@ -2946,20 +3039,23 @@
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V43" s="3">
+      <c r="V43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W43" s="3">
         <v>24500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>60700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>13700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2976,35 +3072,35 @@
         <v>0</v>
       </c>
       <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
         <v>100</v>
-      </c>
-      <c r="I44" s="3">
-        <v>400</v>
       </c>
       <c r="J44" s="3">
         <v>400</v>
       </c>
       <c r="K44" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="L44" s="3">
         <v>200</v>
       </c>
       <c r="M44" s="3">
+        <v>200</v>
+      </c>
+      <c r="N44" s="3">
         <v>100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>200</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3017,34 +3113,37 @@
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V44" s="3">
+      <c r="V44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W44" s="3">
         <v>12100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>22500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>500</v>
       </c>
       <c r="H45" s="3">
         <v>500</v>
@@ -3053,29 +3152,29 @@
         <v>500</v>
       </c>
       <c r="J45" s="3">
+        <v>500</v>
+      </c>
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3088,64 +3187,67 @@
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W45" s="3">
         <v>6500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2300</v>
-      </c>
-      <c r="O46" s="3">
-        <v>2000</v>
       </c>
       <c r="P46" s="3">
         <v>2000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>8</v>
+      <c r="Q46" s="3">
+        <v>2000</v>
       </c>
       <c r="R46" s="3" t="s">
         <v>8</v>
@@ -3159,20 +3261,23 @@
       <c r="U46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W46" s="3">
         <v>87500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>109400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>84400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>91600</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3185,18 +3290,18 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3">
         <v>300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3209,8 +3314,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3242,8 +3347,11 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3251,7 +3359,7 @@
         <v>100</v>
       </c>
       <c r="E48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F48" s="3">
         <v>200</v>
@@ -3260,7 +3368,7 @@
         <v>200</v>
       </c>
       <c r="H48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I48" s="3">
         <v>300</v>
@@ -3269,7 +3377,7 @@
         <v>300</v>
       </c>
       <c r="K48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="L48" s="3">
         <v>400</v>
@@ -3278,7 +3386,7 @@
         <v>400</v>
       </c>
       <c r="N48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="O48" s="3">
         <v>300</v>
@@ -3286,8 +3394,8 @@
       <c r="P48" s="3">
         <v>300</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>8</v>
+      <c r="Q48" s="3">
+        <v>300</v>
       </c>
       <c r="R48" s="3" t="s">
         <v>8</v>
@@ -3301,49 +3409,52 @@
       <c r="U48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W48" s="3">
         <v>188700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>190500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>257100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>259300</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E49" s="3">
         <v>14200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1600</v>
       </c>
-      <c r="I49" s="3">
-        <v>0</v>
-      </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>8</v>
@@ -3351,8 +3462,8 @@
       <c r="N49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P49" s="3">
         <v>0</v>
@@ -3373,19 +3484,22 @@
         <v>0</v>
       </c>
       <c r="V49" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="W49" s="3">
         <v>700</v>
       </c>
       <c r="X49" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y49" s="3">
         <v>43200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>37400</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,20 +3643,23 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E52" s="3">
         <v>2600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1500</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3552,23 +3672,23 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
-        <v>100</v>
+      <c r="K52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>8</v>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>8</v>
@@ -3585,20 +3705,23 @@
       <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W52" s="3">
         <v>5100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,53 +3791,56 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E54" s="3">
         <v>19100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>4300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>4200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2300</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>8</v>
       </c>
@@ -3727,20 +3853,23 @@
       <c r="U54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W54" s="3">
         <v>282100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>307400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>395500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,13 +3923,14 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
         <v>0</v>
@@ -3808,37 +3939,37 @@
         <v>0</v>
       </c>
       <c r="G57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H57" s="3">
         <v>200</v>
       </c>
       <c r="I57" s="3">
+        <v>200</v>
+      </c>
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L57" s="3">
-        <v>100</v>
+      <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M57" s="3">
         <v>100</v>
       </c>
       <c r="N57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O57" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
+      <c r="Q57" s="3">
+        <v>600</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>8</v>
@@ -3852,64 +3983,67 @@
       <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W57" s="3">
         <v>41600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>40000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>41200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
       </c>
       <c r="F58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>4200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>14800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2200</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
@@ -3923,28 +4057,31 @@
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W58" s="3">
         <v>1200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E59" s="3">
         <v>400</v>
-      </c>
-      <c r="E59" s="3">
-        <v>500</v>
       </c>
       <c r="F59" s="3">
         <v>500</v>
@@ -3953,35 +4090,35 @@
         <v>500</v>
       </c>
       <c r="H59" s="3">
+        <v>500</v>
+      </c>
+      <c r="I59" s="3">
         <v>700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5800</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>8</v>
       </c>
@@ -3994,65 +4131,68 @@
       <c r="U59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
+      <c r="V59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W59" s="3">
         <v>0</v>
       </c>
       <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3">
         <v>300</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E60" s="3">
         <v>700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>18200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>6400</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4065,20 +4205,23 @@
       <c r="U60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W60" s="3">
         <v>42800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>41500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>43100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4113,17 +4256,17 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>7800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7700</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4137,19 +4280,22 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>35000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>47000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>48300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4177,14 +4323,14 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>8</v>
@@ -4198,8 +4344,8 @@
       <c r="R62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -4208,19 +4354,22 @@
         <v>0</v>
       </c>
       <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
         <v>21300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>21900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>29000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,53 +4587,56 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E66" s="3">
         <v>700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1200</v>
-      </c>
-      <c r="I66" s="3">
-        <v>6500</v>
       </c>
       <c r="J66" s="3">
         <v>6500</v>
       </c>
       <c r="K66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="L66" s="3">
         <v>3100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4491,20 +4649,23 @@
       <c r="U66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W66" s="3">
         <v>99100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>110400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>120400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>116600</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4911,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,53 +4985,56 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-39200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-39000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-38000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-36500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-34800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-33600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-31400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-28300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-25400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-23400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-19700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-17100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>8</v>
       </c>
@@ -4873,20 +5047,23 @@
       <c r="U72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W72" s="3">
         <v>-41700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-24600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>46000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,53 +5281,56 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E76" s="3">
         <v>18400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-15600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-14200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5157,20 +5343,23 @@
       <c r="U76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W76" s="3">
         <v>183000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>197000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>275100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>284400</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="V80" s="2">
+      <c r="V80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-2100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-2900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1700</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W81" s="3">
         <v>-17000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-70400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,8 +5612,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5444,11 +5643,11 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -5467,26 +5666,29 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>8</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W83" s="3">
         <v>7200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>15600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>11200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-1100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-4400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1100</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W89" s="3">
         <v>31300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-4700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>30400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,19 +6158,20 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
         <v>0</v>
       </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
+      <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -5974,43 +6195,46 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O91" s="3">
         <v>-100</v>
       </c>
       <c r="P91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>8</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V91" s="3">
-        <v>-100</v>
+      <c r="V91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W91" s="3">
         <v>-100</v>
       </c>
       <c r="X91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,29 +6378,32 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1500</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
       <c r="G94" s="3">
         <v>0</v>
       </c>
       <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
@@ -6181,49 +6411,52 @@
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O94" s="3">
         <v>-100</v>
       </c>
       <c r="P94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>8</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W94" s="3">
         <v>-3600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-11300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-14600</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6482,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6278,8 +6512,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6318,10 +6552,13 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,217 +6776,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E100" s="3">
         <v>1500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>100</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>3100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>5900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1400</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W100" s="3">
         <v>-13800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-8000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-13300</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="M101" s="3">
         <v>-200</v>
       </c>
       <c r="N101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>8</v>
+      <c r="T101" s="3">
+        <v>0</v>
       </c>
       <c r="U101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V101" s="3">
+      <c r="V101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
-      </c>
-      <c r="E102" s="3">
-        <v>-100</v>
       </c>
       <c r="F102" s="3">
         <v>-100</v>
       </c>
       <c r="G102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>300</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W102" s="3">
         <v>14000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-12000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>11300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-12400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="92">
   <si>
     <t>TGL</t>
   </si>
@@ -1244,7 +1244,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2400</v>
+        <v>1800</v>
       </c>
       <c r="E21" s="3">
         <v>-700</v>
@@ -2912,7 +2912,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E42" s="3">
         <v>500</v>
@@ -2986,7 +2986,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>10100</v>
+        <v>9100</v>
       </c>
       <c r="E43" s="3">
         <v>1100</v>
@@ -3133,8 +3133,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>900</v>
       </c>
       <c r="E45" s="3">
         <v>300</v>
@@ -4078,7 +4078,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1100</v>
+        <v>900</v>
       </c>
       <c r="E59" s="3">
         <v>400</v>

--- a/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
   <si>
     <t>TGL</t>
   </si>
@@ -656,286 +656,295 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Y7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>36000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>16200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>21100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>42300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>100</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z8" s="3">
         <v>14800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>67900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>36600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>40100</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E9" s="3">
         <v>200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
       <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>18000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>35700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>16000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>42100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>300</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="X9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z9" s="3">
         <v>13300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>29600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>19400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -943,58 +952,58 @@
         <v>0</v>
       </c>
       <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>500</v>
-      </c>
-      <c r="G10" s="3">
-        <v>200</v>
       </c>
       <c r="H10" s="3">
         <v>200</v>
       </c>
       <c r="I10" s="3">
+        <v>200</v>
+      </c>
+      <c r="J10" s="3">
         <v>100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>200</v>
-      </c>
-      <c r="M10" s="3">
-        <v>100</v>
       </c>
       <c r="N10" s="3">
         <v>100</v>
       </c>
       <c r="O10" s="3">
+        <v>100</v>
+      </c>
+      <c r="P10" s="3">
         <v>300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>200</v>
       </c>
-      <c r="R10" s="3">
-        <v>0</v>
-      </c>
       <c r="S10" s="3">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3">
         <v>200</v>
       </c>
-      <c r="T10" s="3">
-        <v>0</v>
-      </c>
       <c r="U10" s="3">
         <v>0</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>8</v>
+      <c r="V10" s="3">
+        <v>0</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>8</v>
@@ -1002,20 +1011,23 @@
       <c r="X10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="3">
         <v>1500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>38300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>17200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1044,20 +1056,21 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
         <v>800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>100</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
       <c r="G12" s="3">
         <v>0</v>
       </c>
@@ -1065,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
-      </c>
-      <c r="K12" s="3">
-        <v>100</v>
       </c>
       <c r="L12" s="3">
         <v>100</v>
@@ -1083,32 +1096,32 @@
         <v>100</v>
       </c>
       <c r="O12" s="3">
+        <v>100</v>
+      </c>
+      <c r="P12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>100</v>
       </c>
-      <c r="Q12" s="3">
-        <v>0</v>
-      </c>
       <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
         <v>100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>200</v>
-      </c>
-      <c r="T12" s="3">
-        <v>100</v>
       </c>
       <c r="U12" s="3">
         <v>100</v>
       </c>
       <c r="V12" s="3">
+        <v>100</v>
+      </c>
+      <c r="W12" s="3">
         <v>200</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1124,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1204,46 +1220,49 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
         <v>19500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-500</v>
-      </c>
-      <c r="H14" s="3">
-        <v>100</v>
       </c>
       <c r="I14" s="3">
         <v>100</v>
       </c>
       <c r="J14" s="3">
+        <v>100</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1276,21 +1295,24 @@
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>93700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -1353,19 +1375,22 @@
         <v>0</v>
       </c>
       <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3">
         <v>7200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>15600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>11200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1391,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1000</v>
       </c>
       <c r="H17" s="3">
         <v>1000</v>
       </c>
       <c r="I17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J17" s="3">
         <v>2000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>40700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>47700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1800</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z17" s="3">
         <v>26100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>142200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>36400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3700</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
       <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
         <v>-700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-2700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1700</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-74300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1581,38 +1613,39 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1620,129 +1653,135 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>-1000</v>
       </c>
       <c r="Q20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R20" s="3">
         <v>-300</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-200</v>
       </c>
       <c r="S20" s="3">
         <v>-200</v>
       </c>
       <c r="T20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>8</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>10800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-1400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-3600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1700</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-47900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1785,138 +1824,144 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R22" s="3">
-        <v>400</v>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S22" s="3">
         <v>400</v>
       </c>
       <c r="T22" s="3">
+        <v>400</v>
+      </c>
+      <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
-      </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z22" s="3">
         <v>800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-23100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1700</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-13900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-64500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -1924,21 +1969,21 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1963,26 +2008,29 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>8</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z24" s="3">
         <v>3100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2061,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-23500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1700</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-17000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-70400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-23500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1700</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-17000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-70400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2301,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2381,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2461,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2541,38 +2607,41 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2580,129 +2649,135 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>1000</v>
       </c>
       <c r="Q32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R32" s="3">
         <v>300</v>
-      </c>
-      <c r="R32" s="3">
-        <v>200</v>
       </c>
       <c r="S32" s="3">
         <v>200</v>
       </c>
       <c r="T32" s="3">
+        <v>200</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>8</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z32" s="3">
         <v>1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-23500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1700</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-17000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-70400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2781,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-23500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1700</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-17000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-70400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Y38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2976,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3006,62 +3091,63 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E41" s="3">
         <v>1300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200</v>
-      </c>
-      <c r="F41" s="3">
-        <v>300</v>
       </c>
       <c r="G41" s="3">
         <v>300</v>
       </c>
       <c r="H41" s="3">
+        <v>300</v>
+      </c>
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1600</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3074,20 +3160,23 @@
       <c r="X41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z41" s="3">
         <v>44400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>30400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>42600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3098,19 +3187,19 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>300</v>
-      </c>
-      <c r="J42" s="3">
-        <v>100</v>
       </c>
       <c r="K42" s="3">
         <v>100</v>
@@ -3122,7 +3211,7 @@
         <v>100</v>
       </c>
       <c r="N42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -3166,34 +3255,37 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E43" s="3">
         <v>2700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K43" s="3">
         <v>100</v>
-      </c>
-      <c r="K43" s="3">
-        <v>200</v>
       </c>
       <c r="L43" s="3">
         <v>200</v>
@@ -3202,14 +3294,14 @@
         <v>200</v>
       </c>
       <c r="N43" s="3">
+        <v>200</v>
+      </c>
+      <c r="O43" s="3">
         <v>500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -3217,11 +3309,11 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3234,25 +3326,28 @@
       <c r="X43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z43" s="3">
         <v>24500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>60700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>13700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E44" s="3">
         <v>0</v>
@@ -3273,35 +3368,35 @@
         <v>0</v>
       </c>
       <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3">
         <v>100</v>
-      </c>
-      <c r="L44" s="3">
-        <v>400</v>
       </c>
       <c r="M44" s="3">
         <v>400</v>
       </c>
       <c r="N44" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="O44" s="3">
         <v>200</v>
       </c>
       <c r="P44" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q44" s="3">
         <v>100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>200</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3314,20 +3409,23 @@
       <c r="X44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z44" s="3">
         <v>12100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>7900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>22500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3338,19 +3436,19 @@
         <v>300</v>
       </c>
       <c r="F45" s="3">
+        <v>300</v>
+      </c>
+      <c r="G45" s="3">
         <v>900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>500</v>
       </c>
       <c r="K45" s="3">
         <v>500</v>
@@ -3359,29 +3457,29 @@
         <v>500</v>
       </c>
       <c r="M45" s="3">
+        <v>500</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3394,73 +3492,76 @@
       <c r="X45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z45" s="3">
         <v>6500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2300</v>
-      </c>
-      <c r="R46" s="3">
-        <v>2000</v>
       </c>
       <c r="S46" s="3">
         <v>2000</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>8</v>
+      <c r="T46" s="3">
+        <v>2000</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>8</v>
@@ -3474,20 +3575,23 @@
       <c r="X46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z46" s="3">
         <v>87500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>109400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>84400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>91600</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3509,18 +3613,18 @@
       <c r="I47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
         <v>300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1100</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3533,8 +3637,8 @@
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3566,25 +3670,28 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E48" s="3">
         <v>800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>200</v>
-      </c>
-      <c r="F48" s="3">
-        <v>100</v>
       </c>
       <c r="G48" s="3">
         <v>100</v>
       </c>
       <c r="H48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I48" s="3">
         <v>200</v>
@@ -3593,7 +3700,7 @@
         <v>200</v>
       </c>
       <c r="K48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L48" s="3">
         <v>300</v>
@@ -3602,7 +3709,7 @@
         <v>300</v>
       </c>
       <c r="N48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O48" s="3">
         <v>400</v>
@@ -3611,7 +3718,7 @@
         <v>400</v>
       </c>
       <c r="Q48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="R48" s="3">
         <v>300</v>
@@ -3619,8 +3726,8 @@
       <c r="S48" s="3">
         <v>300</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>8</v>
+      <c r="T48" s="3">
+        <v>300</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>8</v>
@@ -3634,58 +3741,61 @@
       <c r="X48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z48" s="3">
         <v>188700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>190500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>257100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>259300</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
         <v>3000</v>
       </c>
       <c r="F49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G49" s="3">
         <v>15200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>14200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1600</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
+      <c r="O49" s="3">
+        <v>0</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>8</v>
@@ -3693,8 +3803,8 @@
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -3715,19 +3825,22 @@
         <v>0</v>
       </c>
       <c r="Y49" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="3">
         <v>700</v>
       </c>
       <c r="AA49" s="3">
+        <v>700</v>
+      </c>
+      <c r="AB49" s="3">
         <v>43200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>37400</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3806,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3886,29 +4002,32 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E52" s="3">
         <v>8400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1500</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
@@ -3921,23 +4040,23 @@
       <c r="M52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="3">
-        <v>100</v>
+      <c r="N52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O52" s="3">
         <v>100</v>
       </c>
       <c r="P52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>8</v>
+      <c r="S52" s="3">
+        <v>0</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>8</v>
@@ -3954,20 +4073,23 @@
       <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z52" s="3">
         <v>5100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4046,62 +4168,65 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E54" s="3">
         <v>16600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2300</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4114,20 +4239,23 @@
       <c r="X54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z54" s="3">
         <v>282100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>307400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>395500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4156,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4186,8 +4315,9 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4198,11 +4328,11 @@
         <v>0</v>
       </c>
       <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
       <c r="H57" s="3">
         <v>0</v>
       </c>
@@ -4210,37 +4340,37 @@
         <v>0</v>
       </c>
       <c r="J57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K57" s="3">
         <v>200</v>
       </c>
       <c r="L57" s="3">
+        <v>200</v>
+      </c>
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O57" s="3">
-        <v>100</v>
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P57" s="3">
         <v>100</v>
       </c>
       <c r="Q57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="S57" s="3">
         <v>600</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>8</v>
+      <c r="T57" s="3">
+        <v>600</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>8</v>
@@ -4254,20 +4384,23 @@
       <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z57" s="3">
         <v>41600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>40000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>41200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4281,46 +4414,46 @@
         <v>100</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>100</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>4200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2500</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>14800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2200</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
+      <c r="T58" s="3">
+        <v>0</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
@@ -4334,20 +4467,23 @@
       <c r="X58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z58" s="3">
         <v>1200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4358,13 +4494,13 @@
         <v>400</v>
       </c>
       <c r="F59" s="3">
+        <v>400</v>
+      </c>
+      <c r="G59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>500</v>
       </c>
       <c r="I59" s="3">
         <v>500</v>
@@ -4373,35 +4509,35 @@
         <v>500</v>
       </c>
       <c r="K59" s="3">
+        <v>500</v>
+      </c>
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5800</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4414,74 +4550,77 @@
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
       </c>
       <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="3">
         <v>300</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E60" s="3">
         <v>3500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>8800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6400</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4494,31 +4633,34 @@
       <c r="X60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z60" s="3">
         <v>42800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>41500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>43100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G61" s="3">
         <v>0</v>
@@ -4551,17 +4693,17 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7700</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4575,31 +4717,34 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>35000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>47000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>48300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4624,14 +4769,14 @@
       <c r="N62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>8</v>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>8</v>
@@ -4645,8 +4790,8 @@
       <c r="U62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -4655,19 +4800,22 @@
         <v>0</v>
       </c>
       <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="3">
         <v>21300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>21900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>29000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4746,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4826,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4906,62 +5060,65 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E66" s="3">
         <v>4600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1200</v>
-      </c>
-      <c r="L66" s="3">
-        <v>6500</v>
       </c>
       <c r="M66" s="3">
         <v>6500</v>
       </c>
       <c r="N66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="O66" s="3">
         <v>3100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14200</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>8</v>
       </c>
@@ -4974,20 +5131,23 @@
       <c r="X66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z66" s="3">
         <v>99100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>110400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>120400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>116600</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5016,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5096,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5176,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5256,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5336,62 +5506,65 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-63500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-61400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-38000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-39200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-39000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-38000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-36500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-34800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-33600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-31400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-28300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-25400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-19700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-17100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-13900</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5404,20 +5577,23 @@
       <c r="X72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z72" s="3">
         <v>-41700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-24600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>46000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5496,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5576,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5656,62 +5838,65 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E76" s="3">
         <v>12000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>29100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>18400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-15600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-14200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-11900</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5724,20 +5909,23 @@
       <c r="X76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z76" s="3">
         <v>183000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>197000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>275100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>284400</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5816,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Y80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-23500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1700</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-17000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-70400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6011,8 +6208,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6050,11 +6248,11 @@
         <v>0</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
         <v>100</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -6073,26 +6271,29 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>8</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z83" s="3">
         <v>7200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>15600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>11200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6171,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6251,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6331,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6411,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6491,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-4400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1100</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z89" s="3">
         <v>31300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>30400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6601,28 +6820,29 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -6646,43 +6866,46 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R91" s="3">
         <v>-100</v>
       </c>
       <c r="S91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y91" s="3">
-        <v>-100</v>
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z91" s="3">
         <v>-100</v>
       </c>
       <c r="AA91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6761,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6841,38 +7067,41 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
       <c r="J94" s="3">
         <v>0</v>
       </c>
       <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
         <v>0</v>
       </c>
@@ -6880,49 +7109,52 @@
         <v>0</v>
       </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>8</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-14600</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6951,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6989,8 +7222,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7029,10 +7262,13 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7111,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7191,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7271,244 +7513,256 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E100" s="3">
         <v>3500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>7800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1400</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-13800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-13300</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
-      </c>
-      <c r="E101" s="3">
-        <v>100</v>
       </c>
       <c r="F101" s="3">
         <v>100</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="P101" s="3">
         <v>-200</v>
       </c>
       <c r="Q101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3" t="s">
-        <v>8</v>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>1000</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
         <v>0</v>
       </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>200</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-100</v>
       </c>
       <c r="I102" s="3">
         <v>-100</v>
       </c>
       <c r="J102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>-1300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>300</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z102" s="3">
         <v>14000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>11300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-12400</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TGL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="92">
   <si>
     <t>TGL</t>
   </si>
@@ -656,295 +656,305 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="Z7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>36000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>21100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>42300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>100</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="Z8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA8" s="3">
         <v>14800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>67900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>36600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>40100</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
       <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>18000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>35700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>15500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>42100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>13600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>300</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Y9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA9" s="3">
         <v>13300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>29600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>19400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -955,58 +965,58 @@
         <v>0</v>
       </c>
       <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
         <v>800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>500</v>
-      </c>
-      <c r="H10" s="3">
-        <v>200</v>
       </c>
       <c r="I10" s="3">
         <v>200</v>
       </c>
       <c r="J10" s="3">
+        <v>200</v>
+      </c>
+      <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>200</v>
-      </c>
-      <c r="N10" s="3">
-        <v>100</v>
       </c>
       <c r="O10" s="3">
         <v>100</v>
       </c>
       <c r="P10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="3">
         <v>300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>200</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
       <c r="T10" s="3">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3">
         <v>200</v>
       </c>
-      <c r="U10" s="3">
-        <v>0</v>
-      </c>
       <c r="V10" s="3">
         <v>0</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>8</v>
+      <c r="W10" s="3">
+        <v>0</v>
       </c>
       <c r="X10" s="3" t="s">
         <v>8</v>
@@ -1014,20 +1024,23 @@
       <c r="Y10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA10" s="3">
         <v>1500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>38300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>17200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,23 +1070,24 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
         <v>800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>100</v>
       </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
       <c r="H12" s="3">
         <v>0</v>
       </c>
@@ -1081,13 +1095,13 @@
         <v>0</v>
       </c>
       <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>100</v>
       </c>
       <c r="M12" s="3">
         <v>100</v>
@@ -1099,32 +1113,32 @@
         <v>100</v>
       </c>
       <c r="P12" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q12" s="3">
         <v>300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>100</v>
       </c>
-      <c r="R12" s="3">
-        <v>0</v>
-      </c>
       <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3">
         <v>100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>200</v>
-      </c>
-      <c r="U12" s="3">
-        <v>100</v>
       </c>
       <c r="V12" s="3">
         <v>100</v>
       </c>
       <c r="W12" s="3">
+        <v>100</v>
+      </c>
+      <c r="X12" s="3">
         <v>200</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1140,8 +1154,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,49 +1240,52 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>19500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-500</v>
-      </c>
-      <c r="I14" s="3">
-        <v>100</v>
       </c>
       <c r="J14" s="3">
         <v>100</v>
       </c>
       <c r="K14" s="3">
+        <v>100</v>
+      </c>
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1298,25 +1318,28 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>93700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
         <v>100</v>
       </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
@@ -1378,19 +1401,22 @@
         <v>0</v>
       </c>
       <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
         <v>7200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>15600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>11200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,8 +1443,9 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1426,165 +1453,171 @@
         <v>5700</v>
       </c>
       <c r="E17" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F17" s="3">
         <v>1900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>700</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1000</v>
       </c>
       <c r="I17" s="3">
         <v>1000</v>
       </c>
       <c r="J17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K17" s="3">
         <v>2000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>47700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1800</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA17" s="3">
         <v>26100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>142200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>36400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>30200</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3700</v>
       </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
       <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
         <v>-700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-1700</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-74300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9900</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,41 +1647,42 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1656,132 +1690,138 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3">
         <v>-1000</v>
       </c>
       <c r="R20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S20" s="3">
         <v>-300</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-200</v>
       </c>
       <c r="T20" s="3">
         <v>-200</v>
       </c>
       <c r="U20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>8</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>10800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-2100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-1300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-2900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-3600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1700</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-47900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1827,144 +1867,150 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S22" s="3">
-        <v>400</v>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T22" s="3">
         <v>400</v>
       </c>
       <c r="U22" s="3">
+        <v>400</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
         <v>800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>1200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-23100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-1700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1700</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-13900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-64500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="E24" s="3">
+        <v>100</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I24" s="3">
         <v>0</v>
@@ -1972,21 +2018,21 @@
       <c r="J24" s="3">
         <v>0</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -2011,26 +2057,29 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>8</v>
+      <c r="X24" s="3">
+        <v>0</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA24" s="3">
         <v>3100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>8200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1700</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-17000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-70400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-10500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-23500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1700</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-17000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-70400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-10500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,41 +2677,44 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>4700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2652,132 +2722,138 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="3">
         <v>1000</v>
       </c>
       <c r="R32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S32" s="3">
         <v>300</v>
-      </c>
-      <c r="S32" s="3">
-        <v>200</v>
       </c>
       <c r="T32" s="3">
         <v>200</v>
       </c>
       <c r="U32" s="3">
+        <v>200</v>
+      </c>
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>8</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA32" s="3">
         <v>1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3400</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-23500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1700</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-17000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-70400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-10500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-23500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1700</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-17000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-70400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-10500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="Z38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,65 +3178,66 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E41" s="3">
         <v>5500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>300</v>
       </c>
       <c r="H41" s="3">
         <v>300</v>
       </c>
       <c r="I41" s="3">
+        <v>300</v>
+      </c>
+      <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>4600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1600</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>8</v>
       </c>
@@ -3163,20 +3250,23 @@
       <c r="Y41" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA41" s="3">
         <v>44400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>30400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>42600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>31400</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3190,19 +3280,19 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>300</v>
-      </c>
-      <c r="K42" s="3">
-        <v>100</v>
       </c>
       <c r="L42" s="3">
         <v>100</v>
@@ -3214,7 +3304,7 @@
         <v>100</v>
       </c>
       <c r="O42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -3258,37 +3348,40 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E43" s="3">
         <v>11100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K43" s="3">
+      <c r="K43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L43" s="3">
         <v>100</v>
-      </c>
-      <c r="L43" s="3">
-        <v>200</v>
       </c>
       <c r="M43" s="3">
         <v>200</v>
@@ -3297,14 +3390,14 @@
         <v>200</v>
       </c>
       <c r="O43" s="3">
+        <v>200</v>
+      </c>
+      <c r="P43" s="3">
         <v>500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>300</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -3312,11 +3405,11 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>8</v>
       </c>
@@ -3329,29 +3422,32 @@
       <c r="Y43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="Z43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA43" s="3">
         <v>24500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>60700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>13700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
         <v>100</v>
       </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
       <c r="F44" s="3">
         <v>0</v>
       </c>
@@ -3371,35 +3467,35 @@
         <v>0</v>
       </c>
       <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
         <v>100</v>
-      </c>
-      <c r="M44" s="3">
-        <v>400</v>
       </c>
       <c r="N44" s="3">
         <v>400</v>
       </c>
       <c r="O44" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="P44" s="3">
         <v>200</v>
       </c>
       <c r="Q44" s="3">
+        <v>200</v>
+      </c>
+      <c r="R44" s="3">
         <v>100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>200</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>8</v>
       </c>
@@ -3412,25 +3508,28 @@
       <c r="Y44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="Z44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA44" s="3">
         <v>12100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>7900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>22500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="E45" s="3">
         <v>300</v>
@@ -3439,19 +3538,19 @@
         <v>300</v>
       </c>
       <c r="G45" s="3">
+        <v>300</v>
+      </c>
+      <c r="H45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>400</v>
-      </c>
-      <c r="K45" s="3">
-        <v>500</v>
       </c>
       <c r="L45" s="3">
         <v>500</v>
@@ -3460,29 +3559,29 @@
         <v>500</v>
       </c>
       <c r="N45" s="3">
+        <v>500</v>
+      </c>
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>8</v>
       </c>
@@ -3495,76 +3594,79 @@
       <c r="Y45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA45" s="3">
         <v>6500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>10500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E46" s="3">
         <v>17000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2300</v>
-      </c>
-      <c r="S46" s="3">
-        <v>2000</v>
       </c>
       <c r="T46" s="3">
         <v>2000</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>8</v>
+      <c r="U46" s="3">
+        <v>2000</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>8</v>
@@ -3578,20 +3680,23 @@
       <c r="Y46" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="Z46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA46" s="3">
         <v>87500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>109400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>84400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>91600</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3616,18 +3721,18 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3">
         <v>300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
@@ -3640,8 +3745,8 @@
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -3673,28 +3778,31 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>100</v>
+      </c>
+      <c r="E48" s="3">
         <v>1100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>100</v>
       </c>
       <c r="H48" s="3">
         <v>100</v>
       </c>
       <c r="I48" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>200</v>
@@ -3703,7 +3811,7 @@
         <v>200</v>
       </c>
       <c r="L48" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M48" s="3">
         <v>300</v>
@@ -3712,7 +3820,7 @@
         <v>300</v>
       </c>
       <c r="O48" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P48" s="3">
         <v>400</v>
@@ -3721,7 +3829,7 @@
         <v>400</v>
       </c>
       <c r="R48" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S48" s="3">
         <v>300</v>
@@ -3729,8 +3837,8 @@
       <c r="T48" s="3">
         <v>300</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>8</v>
+      <c r="U48" s="3">
+        <v>300</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>8</v>
@@ -3744,20 +3852,23 @@
       <c r="Y48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA48" s="3">
         <v>188700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>190500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>257100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>259300</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3765,40 +3876,40 @@
         <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>3000</v>
       </c>
       <c r="G49" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H49" s="3">
         <v>15200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1600</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
       <c r="N49" s="3">
         <v>0</v>
       </c>
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>8</v>
@@ -3806,8 +3917,8 @@
       <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3828,19 +3939,22 @@
         <v>0</v>
       </c>
       <c r="Z49" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="3">
         <v>700</v>
       </c>
       <c r="AB49" s="3">
+        <v>700</v>
+      </c>
+      <c r="AC49" s="3">
         <v>43200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>37400</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,32 +4122,35 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E52" s="3">
         <v>6100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1500</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
@@ -4043,23 +4163,23 @@
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
-        <v>100</v>
+      <c r="O52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P52" s="3">
         <v>100</v>
       </c>
       <c r="Q52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>8</v>
+      <c r="T52" s="3">
+        <v>0</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>8</v>
@@ -4076,20 +4196,23 @@
       <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA52" s="3">
         <v>5100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,65 +4294,68 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21600</v>
+      </c>
+      <c r="E54" s="3">
         <v>24200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>30400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>7100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2300</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>8</v>
       </c>
@@ -4242,20 +4368,23 @@
       <c r="Y54" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA54" s="3">
         <v>282100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>307400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>395500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>401000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,8 +4446,9 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4331,11 +4462,11 @@
         <v>0</v>
       </c>
       <c r="G57" s="3">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3">
         <v>200</v>
       </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
       <c r="I57" s="3">
         <v>0</v>
       </c>
@@ -4343,37 +4474,37 @@
         <v>0</v>
       </c>
       <c r="K57" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="L57" s="3">
         <v>200</v>
       </c>
       <c r="M57" s="3">
+        <v>200</v>
+      </c>
+      <c r="N57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P57" s="3">
-        <v>100</v>
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q57" s="3">
         <v>100</v>
       </c>
       <c r="R57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S57" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>8</v>
+      <c r="U57" s="3">
+        <v>600</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>8</v>
@@ -4387,20 +4518,23 @@
       <c r="Y57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA57" s="3">
         <v>41600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>40000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>41200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4417,46 +4551,46 @@
         <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>100</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>4200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2500</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>14800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2200</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>8</v>
+      <c r="U58" s="3">
+        <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
@@ -4470,20 +4604,23 @@
       <c r="Y58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA58" s="3">
         <v>1200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1700</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4497,13 +4634,13 @@
         <v>400</v>
       </c>
       <c r="G59" s="3">
+        <v>400</v>
+      </c>
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>500</v>
       </c>
       <c r="J59" s="3">
         <v>500</v>
@@ -4512,35 +4649,35 @@
         <v>500</v>
       </c>
       <c r="L59" s="3">
+        <v>500</v>
+      </c>
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5800</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>8</v>
       </c>
@@ -4553,77 +4690,80 @@
       <c r="Y59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
+      <c r="Z59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
       </c>
       <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3">
         <v>300</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E60" s="3">
         <v>3900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>8800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>6400</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>8</v>
       </c>
@@ -4636,20 +4776,23 @@
       <c r="Y60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="Z60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA60" s="3">
         <v>42800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>41500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>43100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>31100</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4657,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -4696,17 +4839,17 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7700</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4720,34 +4863,37 @@
         <v>0</v>
       </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>35000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>47000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>48300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>54600</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>8</v>
       </c>
@@ -4772,14 +4918,14 @@
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>8</v>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>8</v>
@@ -4793,8 +4939,8 @@
       <c r="V62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
@@ -4803,19 +4949,22 @@
         <v>0</v>
       </c>
       <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3">
         <v>21300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>21900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>29000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,65 +5218,68 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E66" s="3">
         <v>6300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1200</v>
-      </c>
-      <c r="M66" s="3">
-        <v>6500</v>
       </c>
       <c r="N66" s="3">
         <v>6500</v>
       </c>
       <c r="O66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="P66" s="3">
         <v>3100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>18300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14200</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>8</v>
       </c>
@@ -5134,20 +5292,23 @@
       <c r="Y66" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA66" s="3">
         <v>99100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>110400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>120400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>116600</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,65 +5680,68 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-69000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-66700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-63500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-61400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-38000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-39200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-39000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-38000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-36500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-34800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-33600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-31400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-28300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-23400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-19700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-17100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-13900</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>8</v>
       </c>
@@ -5580,20 +5754,23 @@
       <c r="Y72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA72" s="3">
         <v>-41700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-24600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>46000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,65 +6024,68 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E76" s="3">
         <v>18000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>29100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>18400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-15600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-14200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-11900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>8</v>
       </c>
@@ -5912,20 +6098,23 @@
       <c r="Y76" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="Z76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA76" s="3">
         <v>183000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>197000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>275100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>284400</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="Z80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-23500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1700</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-17000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-70400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-10500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6251,11 +6450,11 @@
         <v>0</v>
       </c>
       <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
         <v>100</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -6274,26 +6473,29 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>8</v>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA83" s="3">
         <v>7200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>15600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>11200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>10500</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6921,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-3000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-4400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1100</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA89" s="3">
         <v>31300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>30400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>15400</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,31 +7041,32 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6869,43 +7090,46 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S91" s="3">
         <v>-100</v>
       </c>
       <c r="T91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>8</v>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z91" s="3">
-        <v>-100</v>
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA91" s="3">
         <v>-100</v>
       </c>
       <c r="AB91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,41 +7297,44 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1500</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
       <c r="K94" s="3">
         <v>0</v>
       </c>
       <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
         <v>0</v>
       </c>
@@ -7112,49 +7342,52 @@
         <v>0</v>
       </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S94" s="3">
         <v>-100</v>
       </c>
       <c r="T94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>8</v>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-14600</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7225,8 +7459,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7265,10 +7499,13 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-3300</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,91 +7759,97 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>100</v>
+      </c>
+      <c r="E100" s="3">
         <v>7500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>7700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>7800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1400</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-13800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-8000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-13300</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7608,161 +7857,167 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
-      </c>
-      <c r="F101" s="3">
-        <v>100</v>
       </c>
       <c r="G101" s="3">
         <v>100</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I101" s="3">
         <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="3">
         <v>-200</v>
       </c>
       <c r="R101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>8</v>
+      <c r="X101" s="3">
+        <v>0</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E102" s="3">
         <v>4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>200</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-100</v>
       </c>
       <c r="J102" s="3">
         <v>-100</v>
       </c>
       <c r="K102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>300</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>-1300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>300</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA102" s="3">
         <v>14000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>11300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-12400</v>
       </c>
     </row>
